--- a/docs/MindX•SDK•6.0.RC3•mxRec•公网地址和邮箱地址.xlsx
+++ b/docs/MindX•SDK•6.0.RC3•mxRec•公网地址和邮箱地址.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WordSummary!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Detail_1!$A$1:$C$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Detail_1!$A$1:$C$208</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="265">
   <si>
     <t>Scan Record ID</t>
   </si>
@@ -680,10 +680,43 @@
     <t>mxrec/README.md</t>
   </si>
   <si>
+    <t>["https://gitee.com/ascend/mxrec/releases"]</t>
+  </si>
+  <si>
+    <t>["https://www.hiascend.com/zh/developer/download/community/result?module=sdk+cann"]</t>
+  </si>
+  <si>
+    <t>["https://www.hiascend.com/developer/download/community/result?module=tf+cann&amp;tf=8.0.RC2.beta1&amp;cann=8.0.RC2.beta1"]</t>
+  </si>
+  <si>
+    <t>["https://www.hiascend.com/hardware/firmware-drivers/community?product=4&amp;model=26&amp;cann=8.0.RC2.beta1&amp;driver=1.0.25.alpha"]</t>
+  </si>
+  <si>
+    <t>["https://www.hiascend.com/document/detail/zh/CANNCommunityEdition/80RC3alpha003/softwareinst/instg/instg_0001.html?Mode=DockerIns&amp;OS=CentOS&amp;Software=cannToolKit"]</t>
+  </si>
+  <si>
+    <t>["https://www.hiascend.com/document/detail/zh/mind-sdk/60rc2/mxRec/mxrecug/mxrecug_0004.html"]</t>
+  </si>
+  <si>
+    <t>["https://www.hiascend.com/developer/ascendhub/detail/mxrec-tf1"]</t>
+  </si>
+  <si>
+    <t>["https://www.hiascend.com/developer/ascendhub/detail/mxrec-tf2"]</t>
+  </si>
+  <si>
+    <t>["http://www.apache.org/licenses/LICENSE-2.0"]</t>
+  </si>
+  <si>
+    <t>["https://gitee.com"]</t>
+  </si>
+  <si>
+    <t>["http://www.apache.org/licenses/"]</t>
+  </si>
+  <si>
     <t>["https://github.com"]</t>
   </si>
   <si>
-    <t>["https://download.open-mpi.org"]</t>
+    <t>["https://download.open-mpi.org/release/open-mpi/v4.1/openmpi-4.1.5.tar.gz"]</t>
   </si>
   <si>
     <t>["https://ascendhub.huawei.com"]</t>
@@ -698,9 +731,6 @@
     <t>["https://github.com/huaweicloud/huaweicloud-sdk-c-obs/archive/refs/tags/v3.23.9.zip"]</t>
   </si>
   <si>
-    <t>["https://download.open-mpi.org/release/open-mpi/v4.1/openmpi-4.1.5.tar.gz"]</t>
-  </si>
-  <si>
     <t>["https://github.com/google/googletest/archive/refs/tags/release-1.8.1.zip"]</t>
   </si>
   <si>
@@ -782,52 +812,28 @@
     <t>["https://storage.googleapis.com/criteo-cail-datasets/day_{`seq -s “,” 0 23`}.gz"]</t>
   </si>
   <si>
-    <t>mxrec/third_party/expected/README.md</t>
-  </si>
-  <si>
-    <t>["https://tl.tartanllama.xyz/en/latest/?badge=latest"]</t>
-  </si>
-  <si>
-    <t>["https://github.com/TartanLlama/expected/actions/workflows/cmake.yml"]</t>
-  </si>
-  <si>
-    <t>["https://ci.appveyor.com/project/TartanLlama/expected"]</t>
-  </si>
-  <si>
-    <t>["https://github.com/microsoft/vcpkg/tree/master/ports/tl-expected"]</t>
-  </si>
-  <si>
-    <t>["https://github.com/yipdw/conan-tl-expected"]</t>
-  </si>
-  <si>
-    <t>["http://www.open-std.org/jtc1/sc22/wg21/docs/papers/2017/p0323r3.pdf"]</t>
-  </si>
-  <si>
-    <t>["http://creativecommons.org/publicdomain/zero/1.0/"]</t>
-  </si>
-  <si>
-    <t>["https://twitter.com/TartanLlama"]</t>
-  </si>
-  <si>
-    <t>mxrec/third_party/expected/CMakeLists.txt</t>
-  </si>
-  <si>
-    <t>["https://tl.tartanllama.xyz"]</t>
-  </si>
-  <si>
-    <t>["https://github.com/catchorg/Catch2/archive/v2.13.10.zip"]</t>
-  </si>
-  <si>
-    <t>mxrec/third_party/expected/include/tl/expected.hpp</t>
-  </si>
-  <si>
-    <t>["http://tl.tartanllama.xyz/"]</t>
-  </si>
-  <si>
-    <t>["https://stackoverflow.com/questions/38288042/c11-14-invoke-workaround"]</t>
-  </si>
-  <si>
-    <t>["https://stackoverflow.com/questions/26744589/what-is-a-proper-way-to-implement-is-swappable-to-test-for-the-swappable-concept"]</t>
+    <t>mxrec/.clang-format</t>
+  </si>
+  <si>
+    <t>["https://clang.llvm.org/docs/ClangFormatStyleOptions.html"]</t>
+  </si>
+  <si>
+    <t>mxrec/docs/build_mxRec_images/centos_build/Dockerfile</t>
+  </si>
+  <si>
+    <t>["https://mirrors.huaweicloud.com/gnu/gmp/gmp-6.1.0.tar.bz2"]</t>
+  </si>
+  <si>
+    <t>["https://mirrors.huaweicloud.com/gnu/mpfr/mpfr-3.1.4.tar.bz2"]</t>
+  </si>
+  <si>
+    <t>["https://mirrors.huaweicloud.com/gnu/mpc/mpc-1.0.3.tar.gz"]</t>
+  </si>
+  <si>
+    <t>["https://mindx.obs.cn-south-1.myhuaweicloud.com/opensource/isl-0.16.1.tar.bz2"]</t>
+  </si>
+  <si>
+    <t>["http://pypi.douban.com/simple/"]</t>
   </si>
 </sst>
 </file>
@@ -840,13 +846,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -857,31 +869,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1443,19 +1436,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1464,153 +1466,138 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1619,34 +1606,34 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2192,188 +2179,188 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:9">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8">
+      <c r="A2" s="6">
         <v>6284</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="7">
         <v>45231.7525694444</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="7">
         <v>45231.7527662037</v>
       </c>
-      <c r="F2" s="8" t="b">
+      <c r="F2" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="6">
         <v>160</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="6">
         <v>158</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="6">
         <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="17"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="15"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="18"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="18"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="18"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="18"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="18"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="18"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="16"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="18"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="16"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="18"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="16"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="18"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="19"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="17"/>
     </row>
     <row r="22" spans="7:7">
-      <c r="G22" s="16"/>
+      <c r="G22" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2398,22 +2385,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2489,7 +2476,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D197"/>
+  <dimension ref="A1:D209"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="108.5" customWidth="1"/>
@@ -2498,2175 +2485,2245 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" ht="16.5" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="B17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="B23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:3">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="B24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:3">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="B30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="B31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="B32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="B34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="B35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="B36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="B38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:3">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="B40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:3">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="B41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:3">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="B42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="B43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="B45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="B46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="B47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:3">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="B48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:3">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="B49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:3">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="B50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:3">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="B51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="B52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="B53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:3">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="B54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:3">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="B55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:3">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="B56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:3">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="B57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:3">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="B58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:3">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="B59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="B60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:3">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="B61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:3">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="B62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:3">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="B63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:3">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="B64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:3">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="B65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:3">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="2" t="s">
+      <c r="B66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:3">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C67" s="2" t="s">
+      <c r="B67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:3">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" s="2" t="s">
+      <c r="B68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:3">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C69" s="2" t="s">
+      <c r="B69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:3">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="B70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:3">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C71" s="2" t="s">
+      <c r="B71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:3">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" s="2" t="s">
+      <c r="B72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:3">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="B73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:3">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" s="2" t="s">
+      <c r="B74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:3">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="B75" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:3">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C76" s="2" t="s">
+      <c r="B76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C77" s="2" t="s">
+      <c r="B77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:3">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C78" s="2" t="s">
+      <c r="B78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:3">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C79" s="2" t="s">
+      <c r="B79" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:3">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80" s="2" t="s">
+      <c r="B80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:3">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" s="2" t="s">
+      <c r="B81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:3">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C82" s="2" t="s">
+      <c r="B82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:3">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C83" s="2" t="s">
+      <c r="B83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:3">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84" s="2" t="s">
+      <c r="B84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:3">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C85" s="2" t="s">
+      <c r="B85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:3">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C86" s="2" t="s">
+      <c r="B86" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:3">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C87" s="2" t="s">
+      <c r="B87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:3">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C88" s="2" t="s">
+      <c r="B88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:3">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C89" s="2" t="s">
+      <c r="B89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:3">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C90" s="2" t="s">
+      <c r="B90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:3">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C91" s="2" t="s">
+      <c r="B91" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:3">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="B92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:3">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C93" s="2" t="s">
+      <c r="B93" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:3">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C94" s="2" t="s">
+      <c r="B94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:3">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C95" s="2" t="s">
+      <c r="B95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:3">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="B96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:3">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="B97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:3">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="B98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:3">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C99" s="2" t="s">
+      <c r="B99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="100" ht="16.5" spans="1:3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C100" s="2" t="s">
+      <c r="B100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="101" ht="16.5" spans="1:3">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C101" s="2" t="s">
+      <c r="B101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="102" ht="16.5" spans="1:3">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C102" s="2" t="s">
+      <c r="B102" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="103" ht="16.5" spans="1:3">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C103" s="2" t="s">
+      <c r="B103" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="104" ht="16.5" spans="1:3">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C104" s="2" t="s">
+      <c r="B104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="105" ht="16.5" spans="1:3">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C105" s="2" t="s">
+      <c r="B105" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="106" ht="16.5" spans="1:3">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C106" s="2" t="s">
+      <c r="B106" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="107" ht="16.5" spans="1:3">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C107" s="2" t="s">
+      <c r="B107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:3">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C108" s="2" t="s">
+      <c r="B108" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="109" ht="16.5" spans="1:3">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C109" s="2" t="s">
+      <c r="B109" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="110" ht="16.5" spans="1:3">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C110" s="2" t="s">
+      <c r="B110" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="111" ht="16.5" spans="1:3">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C111" s="2" t="s">
+      <c r="B111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="112" ht="16.5" spans="1:3">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C112" s="2" t="s">
+      <c r="B112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="113" ht="16.5" spans="1:3">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C113" s="2" t="s">
+      <c r="B113" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="114" ht="16.5" spans="1:3">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C114" s="2" t="s">
+      <c r="B114" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="115" ht="16.5" spans="1:3">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C115" s="2" t="s">
+      <c r="B115" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="116" ht="16.5" spans="1:3">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C116" s="2" t="s">
+      <c r="B116" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="117" ht="16.5" spans="1:3">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C117" s="2" t="s">
+      <c r="B117" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="118" ht="16.5" spans="1:3">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C118" s="2" t="s">
+      <c r="B118" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="119" ht="16.5" spans="1:3">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C119" s="2" t="s">
+      <c r="B119" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="120" ht="16.5" spans="1:3">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C120" s="2" t="s">
+      <c r="B120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="121" ht="16.5" spans="1:3">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C121" s="2" t="s">
+      <c r="B121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="122" ht="16.5" spans="1:3">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C122" s="2" t="s">
+      <c r="B122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="123" ht="16.5" spans="1:3">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C123" s="2" t="s">
+      <c r="B123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="124" ht="16.5" spans="1:3">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C124" s="2" t="s">
+      <c r="B124" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="125" ht="16.5" spans="1:3">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C125" s="2" t="s">
+      <c r="B125" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="1:3">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C126" s="2" t="s">
+      <c r="B126" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="1:3">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C127" s="2" t="s">
+      <c r="B127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:3">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C128" s="2" t="s">
+      <c r="B128" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:3">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C129" s="2" t="s">
+      <c r="B129" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:3">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C130" s="2" t="s">
+      <c r="B130" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:3">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C131" s="2" t="s">
+      <c r="B131" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:3">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C132" s="2" t="s">
+      <c r="B132" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="1:3">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C133" s="2" t="s">
+      <c r="B133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="1:3">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C134" s="2" t="s">
+      <c r="B134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="1:3">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C135" s="2" t="s">
+      <c r="B135" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:3">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C136" s="2" t="s">
+      <c r="B136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:3">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C137" s="2" t="s">
+      <c r="B137" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="1:3">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C138" s="2" t="s">
+      <c r="B138" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="139" ht="16.5" spans="1:3">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C139" s="2" t="s">
+      <c r="B139" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="140" ht="16.5" spans="1:3">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C140" s="2" t="s">
+      <c r="B140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="1:3">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C141" s="2" t="s">
+      <c r="B141" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:3">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C142" s="2" t="s">
+      <c r="B142" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:3">
-      <c r="A143" s="2" t="s">
+      <c r="A143" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C143" s="2" t="s">
+      <c r="B143" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:3">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C144" s="2" t="s">
+      <c r="B144" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:3">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C145" s="2" t="s">
+      <c r="B145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:3">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C146" s="2" t="s">
+      <c r="B146" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="1:3">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C147" s="2" t="s">
+      <c r="B147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="1:3">
-      <c r="A148" s="2" t="s">
+      <c r="A148" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C148" s="2" t="s">
+      <c r="B148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="1:3">
-      <c r="A149" s="2" t="s">
+      <c r="A149" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C149" s="2" t="s">
+      <c r="B149" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:3">
-      <c r="A150" s="2" t="s">
+      <c r="A150" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C150" s="2" t="s">
+      <c r="B150" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:3">
-      <c r="A151" s="2" t="s">
+      <c r="A151" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C151" s="2" t="s">
+      <c r="B151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="1:3">
-      <c r="A152" s="2" t="s">
+      <c r="A152" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C152" s="2" t="s">
+      <c r="B152" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="1:3">
-      <c r="A153" s="2" t="s">
+      <c r="A153" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C153" s="2" t="s">
+      <c r="B153" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C153" s="1" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="1:3">
-      <c r="A154" s="2" t="s">
+      <c r="A154" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C154" s="2" t="s">
+      <c r="B154" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="1:3">
-      <c r="A155" s="2" t="s">
+      <c r="A155" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C155" s="2" t="s">
+      <c r="B155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C155" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="1:3">
-      <c r="A156" s="2" t="s">
+      <c r="A156" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C156" s="2" t="s">
+      <c r="B156" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="1:3">
-      <c r="A157" s="2" t="s">
+      <c r="A157" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C157" s="2" t="s">
+      <c r="B157" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="1:3">
-      <c r="A158" s="2" t="s">
+      <c r="A158" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C158" s="2" t="s">
+      <c r="B158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="1:3">
-      <c r="A159" s="2" t="s">
+      <c r="A159" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C159" s="2" t="s">
+      <c r="B159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="160" ht="16.5" spans="1:3">
-      <c r="A160" s="2" t="s">
+      <c r="A160" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C160" s="2" t="s">
+      <c r="B160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C160" s="1" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="161" ht="16.5" spans="1:3">
-      <c r="A161" s="2" t="s">
+      <c r="A161" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C161" s="2" t="s">
+      <c r="B161" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="1:3">
-      <c r="A162" s="2" t="s">
+      <c r="A162" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C162" s="3" t="s">
+      <c r="B162" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="1:3">
-      <c r="A163" s="4" t="s">
+      <c r="A163" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B163" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C163" s="3" t="s">
+      <c r="B163" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="1:3">
-      <c r="A164" s="4" t="s">
+      <c r="A164" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B164" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C164" s="3" t="s">
+      <c r="B164" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="165" ht="16.5" spans="1:3">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B165" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C165" s="3" t="s">
+      <c r="B165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="166" ht="16.5" spans="1:3">
-      <c r="A166" s="4" t="s">
+      <c r="A166" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B166" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C166" s="3" t="s">
+      <c r="B166" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="1:3">
-      <c r="A167" s="3" t="s">
+      <c r="A167" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B167" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C167" s="3" t="s">
+    </row>
+    <row r="168" ht="16.5" spans="1:3">
+      <c r="A168" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="168" ht="16.5" spans="1:3">
-      <c r="A168" s="3" t="s">
+    <row r="169" ht="16.5" spans="1:3">
+      <c r="A169" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C169" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C168" s="2" t="s">
+    </row>
+    <row r="170" ht="16.5" spans="1:3">
+      <c r="A170" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="169" ht="16.5" spans="1:3">
-      <c r="A169" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C169" s="2" t="s">
+    <row r="171" ht="16.5" spans="1:3">
+      <c r="A171" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="170" ht="16.5" spans="1:3">
-      <c r="A170" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C170" s="2" t="s">
+    <row r="172" ht="16.5" spans="1:3">
+      <c r="A172" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C172" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="171" ht="16.5" spans="1:3">
-      <c r="A171" s="3" t="s">
+    <row r="173" ht="16.5" spans="1:3">
+      <c r="A173" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C171" s="5" t="s">
+    </row>
+    <row r="174" ht="16.5" spans="1:3">
+      <c r="A174" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="172" ht="16.5" spans="1:3">
-      <c r="A172" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C172" s="3" t="s">
+    <row r="175" ht="16.5" spans="1:3">
+      <c r="A175" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="176" ht="16.5" spans="1:3">
+      <c r="A176" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>230</v>
-      </c>
-    </row>
-    <row r="173" ht="16.5" spans="1:3">
-      <c r="A173" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="174" ht="16.5" spans="1:3">
-      <c r="A174" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="175" ht="16.5" spans="1:3">
-      <c r="A175" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="176" ht="16.5" spans="1:3">
-      <c r="A176" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="1:3">
       <c r="A177" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="178" ht="16.5" spans="1:3">
+      <c r="A178" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="179" ht="16.5" spans="1:3">
+      <c r="A179" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="180" ht="16.5" spans="1:3">
+      <c r="A180" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C177" s="3" t="s">
+    </row>
+    <row r="181" ht="16.5" spans="1:3">
+      <c r="A181" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C181" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="178" ht="16.5" spans="1:3">
-      <c r="A178" s="3" t="s">
+    <row r="182" ht="16.5" spans="1:3">
+      <c r="A182" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C178" s="3" t="s">
+      <c r="B182" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C182" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="179" ht="16.5" spans="1:3">
-      <c r="A179" s="3" t="s">
+    <row r="183" ht="16.5" spans="1:3">
+      <c r="A183" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C179" s="3" t="s">
+    </row>
+    <row r="184" ht="16.5" spans="1:3">
+      <c r="A184" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="180" ht="16.5" spans="1:3">
-      <c r="A180" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C180" s="3" t="s">
+    <row r="185" ht="16.5" spans="1:3">
+      <c r="A185" s="1" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="181" ht="16.5" spans="1:3">
-      <c r="A181" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C181" s="3" t="s">
+      <c r="B185" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="182" ht="16.5" spans="1:3">
-      <c r="A182" s="3" t="s">
+    <row r="186" ht="16.5" spans="1:3">
+      <c r="A186" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C182" s="3" t="s">
+    </row>
+    <row r="187" ht="16.5" spans="1:3">
+      <c r="A187" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C187" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="183" ht="16.5" spans="1:3">
-      <c r="A183" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C183" s="3" t="s">
+    <row r="188" ht="16.5" spans="1:3">
+      <c r="A188" s="1" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="184" ht="16.5" spans="1:3">
-      <c r="A184" s="3" t="s">
+      <c r="B188" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C188" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C184" s="3" t="s">
+    </row>
+    <row r="189" ht="16.5" spans="1:3">
+      <c r="A189" s="1" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="185" ht="16.5" spans="1:3">
-      <c r="A185" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C185" s="3" t="s">
+      <c r="B189" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C189" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="186" ht="16.5" spans="1:3">
-      <c r="A186" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C186" s="3" t="s">
+    <row r="190" ht="16.5" spans="1:3">
+      <c r="A190" s="1" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="187" ht="16.5" spans="1:3">
-      <c r="A187" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C187" s="3" t="s">
+      <c r="B190" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C190" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="188" ht="16.5" spans="1:3">
-      <c r="A188" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C188" s="3" t="s">
+    <row r="191" ht="16.5" spans="1:3">
+      <c r="A191" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C191" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="189" ht="16.5" spans="1:3">
-      <c r="A189" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C189" s="3" t="s">
+    <row r="192" ht="16.5" spans="1:3">
+      <c r="A192" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="190" ht="16.5" spans="1:3">
-      <c r="A190" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C190" s="3" t="s">
+    <row r="193" ht="16.5" spans="1:3">
+      <c r="A193" s="1" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="191" ht="16.5" spans="1:3">
-      <c r="A191" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C191" s="3" t="s">
+      <c r="B193" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C193" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="192" ht="16.5" spans="1:3">
-      <c r="A192" s="3" t="s">
+    <row r="194" ht="16.5" spans="1:3">
+      <c r="A194" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B192" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C192" s="3" t="s">
+    </row>
+    <row r="195" s="1" customFormat="1" ht="16.5" spans="1:3">
+      <c r="A195" s="1" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="193" ht="16.5" spans="1:3">
-      <c r="A193" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C193" s="3" t="s">
+      <c r="B195" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C195" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="194" ht="16.5" spans="1:3">
-      <c r="A194" s="3" t="s">
+    <row r="196" ht="16.5" spans="1:3">
+      <c r="A196" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C194" s="3" t="s">
+      <c r="B196" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="195" ht="16.5" spans="1:3">
-      <c r="A195" s="3" t="s">
+    <row r="197" ht="16.5" spans="1:3">
+      <c r="A197" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="196" ht="16.5" spans="1:3">
-      <c r="A196" s="3" t="s">
+      <c r="B197" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="198" ht="16.5" spans="1:3">
+      <c r="A198" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="197" ht="16.5" spans="1:3">
-      <c r="A197" s="3" t="s">
+      <c r="B198" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="199" ht="16.5" spans="1:3">
+      <c r="A199" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>262</v>
-      </c>
-    </row>
+      <c r="B199" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="200" ht="16.5" spans="1:3">
+      <c r="A200" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="201" ht="16.5" spans="1:1">
+      <c r="A201" s="1"/>
+    </row>
+    <row r="202" ht="16.5" spans="1:1">
+      <c r="A202" s="1"/>
+    </row>
+    <row r="203" ht="16.5" spans="1:3">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+    </row>
+    <row r="204" ht="16.5" spans="1:3">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+    </row>
+    <row r="205" ht="16.5" spans="1:3">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+    </row>
+    <row r="206" ht="16.5" spans="1:3">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+    </row>
+    <row r="207" ht="16.5" spans="1:3">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+    </row>
+    <row r="208" ht="16.5" spans="1:3">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+    </row>
+    <row r="209" s="1" customFormat="1" ht="16.5"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C161" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C208" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
